--- a/Result/profitability/4919.xlsx
+++ b/Result/profitability/4919.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>-18.72</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.8825</v>
+        <v>-2.92375</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -772,7 +772,7 @@
         <v>-0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.90125</v>
+        <v>-2.955</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -885,7 +885,7 @@
         <v>-0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.91</v>
+        <v>-3.0475</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -1002,7 +1002,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8575</v>
+        <v>-2.72875</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1119,7 +1119,7 @@
         <v>0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.58</v>
+        <v>-2.5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1240,7 +1240,7 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3825</v>
+        <v>-2.24875</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1365,7 +1365,7 @@
         <v>0.88</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.06625</v>
+        <v>-2.14125</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9542,6 +9542,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>7941</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4922</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3020</v>
+      </c>
+      <c r="F73" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-333</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-4.19%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>212</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-121</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-249</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.615</v>
+      </c>
+      <c r="N73" t="n">
+        <v>37.36875000000001</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-30</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.03355363497712249</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-0.639751552795031</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>3.120000000000005</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0.0893982808022924</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
